--- a/Notas.xlsx
+++ b/Notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binho\Desktop\Curso_R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\binho\Desktop\Curso_R\Curso-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0BE5A1-AA28-4553-B039-0A29712A64BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E9ADB9-625B-49C4-A38B-A33B09196C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="2340" windowWidth="15375" windowHeight="7785" xr2:uid="{2871931E-3673-4404-A8AE-0C2A1D74238E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2871931E-3673-4404-A8AE-0C2A1D74238E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="63">
   <si>
     <t>Mat</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>7.4</t>
+  </si>
+  <si>
+    <t>5.5</t>
   </si>
 </sst>
 </file>
@@ -859,8 +862,8 @@
       <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="5">
-        <v>55</v>
+      <c r="C13" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>52</v>
